--- a/artfynd/A 38317-2021 artfynd.xlsx
+++ b/artfynd/A 38317-2021 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 38317-2021 artfynd.xlsx
+++ b/artfynd/A 38317-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY8"/>
+  <dimension ref="A1:AY9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>112682586</v>
+        <v>112682558</v>
       </c>
       <c r="B2" t="n">
-        <v>55860</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57141</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -720,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>563007</v>
+        <v>563233</v>
       </c>
       <c r="R2" t="n">
-        <v>6352025</v>
+        <v>6351976</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -760,7 +755,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Under tall i anslutning till hällmark</t>
+          <t>På vägen</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -775,7 +770,7 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Samuel Keith</t>
+          <t>Sam Keith</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
@@ -787,15 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>112682587</v>
+        <v>112682559</v>
       </c>
       <c r="B3" t="n">
-        <v>55860</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57141</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -832,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>562956</v>
+        <v>563041</v>
       </c>
       <c r="R3" t="n">
-        <v>6352065</v>
+        <v>6351960</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -870,11 +860,6 @@
           <t>2023-04-13</t>
         </is>
       </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>På hällmark, under bra sittpinne på tall.</t>
-        </is>
-      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
@@ -887,7 +872,7 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Samuel Keith</t>
+          <t>Sam Keith</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
@@ -899,15 +884,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>112682561</v>
+        <v>112682560</v>
       </c>
       <c r="B4" t="n">
-        <v>55860</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57141</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -944,10 +924,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>562981</v>
+        <v>563017</v>
       </c>
       <c r="R4" t="n">
-        <v>6352024</v>
+        <v>6352018</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -994,7 +974,7 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Samuel Keith</t>
+          <t>Sam Keith</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
@@ -1006,15 +986,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>112682566</v>
+        <v>112682561</v>
       </c>
       <c r="B5" t="n">
-        <v>55860</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57141</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1051,10 +1026,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>562923</v>
+        <v>562982</v>
       </c>
       <c r="R5" t="n">
-        <v>6352034</v>
+        <v>6352025</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1089,11 +1064,6 @@
           <t>2023-04-13</t>
         </is>
       </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>På hällmark ner mot sjö.</t>
-        </is>
-      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
@@ -1106,7 +1076,7 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Samuel Keith</t>
+          <t>Sam Keith</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
@@ -1118,15 +1088,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>112682567</v>
+        <v>112682563</v>
       </c>
       <c r="B6" t="n">
-        <v>55860</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57141</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1163,10 +1128,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>563217</v>
+        <v>563008</v>
       </c>
       <c r="R6" t="n">
-        <v>6351844</v>
+        <v>6352025</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1203,7 +1168,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Vid vägen</t>
+          <t>Under tall i anslutning till hällmark</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1218,7 +1183,7 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Samuel Keith</t>
+          <t>Sam Keith</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
@@ -1230,15 +1195,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>112682560</v>
+        <v>112682565</v>
       </c>
       <c r="B7" t="n">
-        <v>55860</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57141</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1275,10 +1235,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>563017</v>
+        <v>562956</v>
       </c>
       <c r="R7" t="n">
-        <v>6352018</v>
+        <v>6352065</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1313,6 +1273,11 @@
           <t>2023-04-13</t>
         </is>
       </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>På hällmark, under bra sittpinne på tall.</t>
+        </is>
+      </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
@@ -1325,7 +1290,7 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Samuel Keith</t>
+          <t>Sam Keith</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
@@ -1337,15 +1302,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>112682582</v>
+        <v>112682566</v>
       </c>
       <c r="B8" t="n">
-        <v>55860</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57141</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1382,10 +1342,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>563040</v>
+        <v>562924</v>
       </c>
       <c r="R8" t="n">
-        <v>6351961</v>
+        <v>6352034</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1420,6 +1380,11 @@
           <t>2023-04-13</t>
         </is>
       </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>På hällmark ner mot sjö.</t>
+        </is>
+      </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
@@ -1432,7 +1397,7 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Samuel Keith</t>
+          <t>Sam Keith</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
@@ -1441,6 +1406,113 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>112682567</v>
+      </c>
+      <c r="B9" t="n">
+        <v>57141</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Ingebo, Sm</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>563217</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6351845</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Oskarshamn</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Döderhult</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2023-04-13</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2023-04-13</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Vid vägen</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Sam Keith</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Håkan Andersson</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
